--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -119,7 +119,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>战神之刃</t>
+    <t>斩仙之刃</t>
   </si>
   <si>
     <t>14,16,15,26</t>
@@ -128,154 +128,316 @@
     <t>5,5,5,5</t>
   </si>
   <si>
-    <t>战神之甲</t>
-  </si>
-  <si>
-    <t>战神之头</t>
-  </si>
-  <si>
-    <t>战神之链</t>
-  </si>
-  <si>
-    <t>战神之镯</t>
-  </si>
-  <si>
-    <t>战神之戒</t>
-  </si>
-  <si>
-    <t>战神之带</t>
-  </si>
-  <si>
-    <t>战神之靴</t>
-  </si>
-  <si>
-    <t>恶魔之杖</t>
+    <t>斩仙之甲</t>
+  </si>
+  <si>
+    <t>斩仙之头</t>
+  </si>
+  <si>
+    <t>斩仙之链</t>
+  </si>
+  <si>
+    <t>斩仙之镯</t>
+  </si>
+  <si>
+    <t>斩仙之戒</t>
+  </si>
+  <si>
+    <t>斩仙之带</t>
+  </si>
+  <si>
+    <t>斩仙之靴</t>
+  </si>
+  <si>
+    <t>魔尊之杖</t>
   </si>
   <si>
     <t>14,16,15,27</t>
   </si>
   <si>
-    <t>恶魔之衣</t>
-  </si>
-  <si>
-    <t>恶魔之头</t>
-  </si>
-  <si>
-    <t>恶魔之链</t>
-  </si>
-  <si>
-    <t>恶魔之镯</t>
-  </si>
-  <si>
-    <t>恶魔之戒</t>
-  </si>
-  <si>
-    <t>恶魔之带</t>
-  </si>
-  <si>
-    <t>恶魔之靴</t>
-  </si>
-  <si>
-    <t>幽灵之剑</t>
+    <t>魔尊之衣</t>
+  </si>
+  <si>
+    <t>魔尊之头</t>
+  </si>
+  <si>
+    <t>魔尊之链</t>
+  </si>
+  <si>
+    <t>魔尊之镯</t>
+  </si>
+  <si>
+    <t>魔尊之戒</t>
+  </si>
+  <si>
+    <t>魔尊之带</t>
+  </si>
+  <si>
+    <t>魔尊之靴</t>
+  </si>
+  <si>
+    <t>幽冥之剑</t>
   </si>
   <si>
     <t>14,16,15,28</t>
   </si>
   <si>
-    <t>幽灵之袍</t>
-  </si>
-  <si>
-    <t>幽灵之头</t>
-  </si>
-  <si>
-    <t>幽灵之链</t>
-  </si>
-  <si>
-    <t>幽灵之镯</t>
-  </si>
-  <si>
-    <t>幽灵之戒</t>
-  </si>
-  <si>
-    <t>幽灵之带</t>
-  </si>
-  <si>
-    <t>幽灵之靴</t>
-  </si>
-  <si>
-    <t>圣战之刃</t>
+    <t>幽冥之袍</t>
+  </si>
+  <si>
+    <t>幽冥之头</t>
+  </si>
+  <si>
+    <t>幽冥之链</t>
+  </si>
+  <si>
+    <t>幽冥之镯</t>
+  </si>
+  <si>
+    <t>幽冥之戒</t>
+  </si>
+  <si>
+    <t>幽冥之带</t>
+  </si>
+  <si>
+    <t>幽冥之靴</t>
+  </si>
+  <si>
+    <t>战魂之刃</t>
   </si>
   <si>
     <t>10,10,10,10</t>
   </si>
   <si>
-    <t>圣战之甲</t>
-  </si>
-  <si>
-    <t>圣战之头</t>
-  </si>
-  <si>
-    <t>圣战之链</t>
-  </si>
-  <si>
-    <t>圣战之镯</t>
-  </si>
-  <si>
-    <t>圣战之戒</t>
-  </si>
-  <si>
-    <t>圣战之带</t>
-  </si>
-  <si>
-    <t>圣战之靴</t>
-  </si>
-  <si>
-    <t>法神之杖</t>
-  </si>
-  <si>
-    <t>法神之衣</t>
-  </si>
-  <si>
-    <t>法神之头</t>
-  </si>
-  <si>
-    <t>法神之链</t>
-  </si>
-  <si>
-    <t>法神之镯</t>
-  </si>
-  <si>
-    <t>法神之戒</t>
-  </si>
-  <si>
-    <t>法神之带</t>
-  </si>
-  <si>
-    <t>法神之靴</t>
-  </si>
-  <si>
-    <t>天尊之剑</t>
-  </si>
-  <si>
-    <t>天尊之袍</t>
-  </si>
-  <si>
-    <t>天尊之头</t>
-  </si>
-  <si>
-    <t>天尊之链</t>
-  </si>
-  <si>
-    <t>天尊之镯</t>
-  </si>
-  <si>
-    <t>天尊之戒</t>
-  </si>
-  <si>
-    <t>天尊之带</t>
-  </si>
-  <si>
-    <t>天尊之靴</t>
+    <t>战魂之甲</t>
+  </si>
+  <si>
+    <t>战魂之头</t>
+  </si>
+  <si>
+    <t>战魂之链</t>
+  </si>
+  <si>
+    <t>战魂之镯</t>
+  </si>
+  <si>
+    <t>战魂之戒</t>
+  </si>
+  <si>
+    <t>战魂之带</t>
+  </si>
+  <si>
+    <t>战魂之靴</t>
+  </si>
+  <si>
+    <t>法魂之杖</t>
+  </si>
+  <si>
+    <t>法魂之衣</t>
+  </si>
+  <si>
+    <t>法魂之头</t>
+  </si>
+  <si>
+    <t>法魂之链</t>
+  </si>
+  <si>
+    <t>法魂之镯</t>
+  </si>
+  <si>
+    <t>法魂之戒</t>
+  </si>
+  <si>
+    <t>法魂之带</t>
+  </si>
+  <si>
+    <t>法魂之靴</t>
+  </si>
+  <si>
+    <t>道魂之剑</t>
+  </si>
+  <si>
+    <t>道魂之袍</t>
+  </si>
+  <si>
+    <t>道魂之头</t>
+  </si>
+  <si>
+    <t>道魂之链</t>
+  </si>
+  <si>
+    <t>道魂之镯</t>
+  </si>
+  <si>
+    <t>道魂之戒</t>
+  </si>
+  <si>
+    <t>道魂之带</t>
+  </si>
+  <si>
+    <t>道魂之靴</t>
+  </si>
+  <si>
+    <t>天神之刃</t>
+  </si>
+  <si>
+    <t>7,8,33,2001</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>天神之甲</t>
+  </si>
+  <si>
+    <t>7,8,34,2002</t>
+  </si>
+  <si>
+    <t>天神之头</t>
+  </si>
+  <si>
+    <t>7,8,35,2002</t>
+  </si>
+  <si>
+    <t>天神之链</t>
+  </si>
+  <si>
+    <t>7,8,9,2003</t>
+  </si>
+  <si>
+    <t>天神之镯</t>
+  </si>
+  <si>
+    <t>7,8,33,2002</t>
+  </si>
+  <si>
+    <t>天神之戒</t>
+  </si>
+  <si>
+    <t>7,8,34,2001</t>
+  </si>
+  <si>
+    <t>天神之带</t>
+  </si>
+  <si>
+    <t>7,8,35,2003</t>
+  </si>
+  <si>
+    <t>天神之靴</t>
+  </si>
+  <si>
+    <t>魔神之杖</t>
+  </si>
+  <si>
+    <t>12,13,33,2001</t>
+  </si>
+  <si>
+    <t>魔神之衣</t>
+  </si>
+  <si>
+    <t>12,13,34,2002</t>
+  </si>
+  <si>
+    <t>魔神之头</t>
+  </si>
+  <si>
+    <t>12,13,35,2002</t>
+  </si>
+  <si>
+    <t>魔神之链</t>
+  </si>
+  <si>
+    <t>12,13,9,2003</t>
+  </si>
+  <si>
+    <t>魔神之镯</t>
+  </si>
+  <si>
+    <t>12,13,33,2002</t>
+  </si>
+  <si>
+    <t>魔神之戒</t>
+  </si>
+  <si>
+    <t>12,13,34,2001</t>
+  </si>
+  <si>
+    <t>魔神之带</t>
+  </si>
+  <si>
+    <t>12,13,35,2003</t>
+  </si>
+  <si>
+    <t>魔神之靴</t>
+  </si>
+  <si>
+    <t>仙神之杖</t>
+  </si>
+  <si>
+    <t>7,33,2004,2007</t>
+  </si>
+  <si>
+    <t>仙神之衣</t>
+  </si>
+  <si>
+    <t>7,34,2005,2008</t>
+  </si>
+  <si>
+    <t>仙神之头</t>
+  </si>
+  <si>
+    <t>7,35,2006,2009</t>
+  </si>
+  <si>
+    <t>仙神之链</t>
+  </si>
+  <si>
+    <t>12,13,2001,2003</t>
+  </si>
+  <si>
+    <t>仙神之镯</t>
+  </si>
+  <si>
+    <t>仙神之戒</t>
+  </si>
+  <si>
+    <t>仙神之带</t>
+  </si>
+  <si>
+    <t>仙神之靴</t>
+  </si>
+  <si>
+    <t>邪神之杖</t>
+  </si>
+  <si>
+    <t>8,33,2004,2007</t>
+  </si>
+  <si>
+    <t>邪神之衣</t>
+  </si>
+  <si>
+    <t>8,34,2005,2008</t>
+  </si>
+  <si>
+    <t>邪神之头</t>
+  </si>
+  <si>
+    <t>8,35,2006,2009</t>
+  </si>
+  <si>
+    <t>邪神之链</t>
+  </si>
+  <si>
+    <t>邪神之镯</t>
+  </si>
+  <si>
+    <t>邪神之戒</t>
+  </si>
+  <si>
+    <t>邪神之带</t>
+  </si>
+  <si>
+    <t>邪神之靴</t>
   </si>
 </sst>
 </file>
@@ -926,7 +1088,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -934,6 +1096,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1254,15 +1417,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="2" customWidth="1"/>
+    <col min="7" max="7" width="12.5083333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.8" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.125" style="2" customWidth="1"/>
     <col min="10" max="10" width="14.875" style="2" customWidth="1"/>
     <col min="11" max="16371" width="9" style="2"/>
@@ -1367,7 +1530,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:10">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1383,17 +1546,17 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1409,17 +1572,17 @@
       <c r="G7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1435,17 +1598,17 @@
       <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1461,17 +1624,17 @@
       <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I9" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1487,17 +1650,17 @@
       <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1513,17 +1676,17 @@
       <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:10">
+      <c r="I11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:10">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1539,17 +1702,17 @@
       <c r="G12" s="1">
         <v>1</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:10">
+      <c r="I12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1565,17 +1728,17 @@
       <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I13" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1591,17 +1754,17 @@
       <c r="G14" s="1">
         <v>2</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1617,17 +1780,17 @@
       <c r="G15" s="1">
         <v>2</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:10">
+      <c r="I15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1643,13 +1806,13 @@
       <c r="G16" s="1">
         <v>2</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="I16" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1669,13 +1832,13 @@
       <c r="G17" s="1">
         <v>2</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17" s="5" t="s">
+      <c r="I17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1695,13 +1858,13 @@
       <c r="G18" s="1">
         <v>2</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="5" t="s">
+      <c r="I18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1721,13 +1884,13 @@
       <c r="G19" s="1">
         <v>2</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="5" t="s">
+      <c r="I19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1747,13 +1910,13 @@
       <c r="G20" s="1">
         <v>2</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="I20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1773,13 +1936,13 @@
       <c r="G21" s="1">
         <v>2</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="I21" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1790,7 +1953,7 @@
       <c r="D22" s="4">
         <v>3000017</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="5" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="1">
@@ -1799,13 +1962,13 @@
       <c r="G22" s="1">
         <v>3</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="I22" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1816,7 +1979,7 @@
       <c r="D23" s="4">
         <v>3000018</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="5" t="s">
         <v>33</v>
       </c>
       <c r="F23" s="1">
@@ -1825,13 +1988,13 @@
       <c r="G23" s="1">
         <v>3</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="I23" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1842,7 +2005,7 @@
       <c r="D24" s="4">
         <v>3000019</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1">
@@ -1851,13 +2014,13 @@
       <c r="G24" s="1">
         <v>3</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="I24" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1868,7 +2031,7 @@
       <c r="D25" s="4">
         <v>3000020</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="5" t="s">
         <v>35</v>
       </c>
       <c r="F25" s="1">
@@ -1877,13 +2040,13 @@
       <c r="G25" s="1">
         <v>3</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="I25" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1894,7 +2057,7 @@
       <c r="D26" s="4">
         <v>3000021</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="1">
@@ -1903,13 +2066,13 @@
       <c r="G26" s="1">
         <v>3</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="I26" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1920,7 +2083,7 @@
       <c r="D27" s="4">
         <v>3000022</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F27" s="1">
@@ -1929,13 +2092,13 @@
       <c r="G27" s="1">
         <v>3</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="I27" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1946,7 +2109,7 @@
       <c r="D28" s="4">
         <v>3000023</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F28" s="1">
@@ -1955,13 +2118,13 @@
       <c r="G28" s="1">
         <v>3</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28" s="5" t="s">
+      <c r="I28" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1972,7 +2135,7 @@
       <c r="D29" s="4">
         <v>3000024</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F29" s="1">
@@ -1981,13 +2144,13 @@
       <c r="G29" s="1">
         <v>3</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29" s="5" t="s">
+      <c r="I29" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2007,13 +2170,13 @@
       <c r="G30" s="1">
         <v>4</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="5" t="s">
+      <c r="I30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J30" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2033,13 +2196,13 @@
       <c r="G31" s="1">
         <v>4</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" s="5" t="s">
+      <c r="I31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2059,13 +2222,13 @@
       <c r="G32" s="1">
         <v>4</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="5" t="s">
+      <c r="I32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J32" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2085,13 +2248,13 @@
       <c r="G33" s="1">
         <v>4</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J33" s="5" t="s">
+      <c r="I33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2111,13 +2274,13 @@
       <c r="G34" s="1">
         <v>4</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J34" s="5" t="s">
+      <c r="I34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J34" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2137,13 +2300,13 @@
       <c r="G35" s="1">
         <v>4</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35" s="5" t="s">
+      <c r="I35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2163,13 +2326,13 @@
       <c r="G36" s="1">
         <v>4</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J36" s="5" t="s">
+      <c r="I36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J36" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2189,13 +2352,13 @@
       <c r="G37" s="1">
         <v>4</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J37" s="5" t="s">
+      <c r="I37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J37" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2215,13 +2378,13 @@
       <c r="G38" s="1">
         <v>5</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J38" s="5" t="s">
+      <c r="I38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2241,13 +2404,13 @@
       <c r="G39" s="1">
         <v>5</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J39" s="5" t="s">
+      <c r="I39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2267,13 +2430,13 @@
       <c r="G40" s="1">
         <v>5</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J40" s="5" t="s">
+      <c r="I40" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J40" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2293,13 +2456,13 @@
       <c r="G41" s="1">
         <v>5</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="5" t="s">
+      <c r="I41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J41" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2319,13 +2482,13 @@
       <c r="G42" s="1">
         <v>5</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J42" s="5" t="s">
+      <c r="I42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J42" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2345,13 +2508,13 @@
       <c r="G43" s="1">
         <v>5</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" s="5" t="s">
+      <c r="I43" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J43" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2371,13 +2534,13 @@
       <c r="G44" s="1">
         <v>5</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J44" s="5" t="s">
+      <c r="I44" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2397,13 +2560,13 @@
       <c r="G45" s="1">
         <v>5</v>
       </c>
-      <c r="H45" s="5" t="s">
+      <c r="H45" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J45" s="5" t="s">
+      <c r="I45" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2423,13 +2586,13 @@
       <c r="G46" s="1">
         <v>6</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J46" s="5" t="s">
+      <c r="I46" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2449,13 +2612,13 @@
       <c r="G47" s="1">
         <v>6</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="H47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J47" s="5" t="s">
+      <c r="I47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J47" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2475,13 +2638,13 @@
       <c r="G48" s="1">
         <v>6</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H48" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J48" s="5" t="s">
+      <c r="I48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J48" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2501,13 +2664,13 @@
       <c r="G49" s="1">
         <v>6</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="5" t="s">
+      <c r="I49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J49" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2527,13 +2690,13 @@
       <c r="G50" s="1">
         <v>6</v>
       </c>
-      <c r="H50" s="5" t="s">
+      <c r="H50" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J50" s="5" t="s">
+      <c r="I50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J50" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2553,13 +2716,13 @@
       <c r="G51" s="1">
         <v>6</v>
       </c>
-      <c r="H51" s="5" t="s">
+      <c r="H51" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J51" s="5" t="s">
+      <c r="I51" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J51" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2579,13 +2742,13 @@
       <c r="G52" s="1">
         <v>6</v>
       </c>
-      <c r="H52" s="5" t="s">
+      <c r="H52" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J52" s="5" t="s">
+      <c r="I52" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J52" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2605,19 +2768,851 @@
       <c r="G53" s="1">
         <v>6</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>41</v>
+      <c r="I53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:10">
+      <c r="C54" s="1">
+        <v>49</v>
+      </c>
+      <c r="D54" s="4">
+        <v>3000049</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1">
+        <v>7</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:10">
+      <c r="C55" s="1">
+        <v>50</v>
+      </c>
+      <c r="D55" s="4">
+        <v>3000050</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="1">
+        <v>2</v>
+      </c>
+      <c r="G55" s="1">
+        <v>7</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:10">
+      <c r="C56" s="1">
+        <v>51</v>
+      </c>
+      <c r="D56" s="4">
+        <v>3000051</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F56" s="1">
+        <v>3</v>
+      </c>
+      <c r="G56" s="1">
+        <v>7</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:10">
+      <c r="C57" s="1">
+        <v>52</v>
+      </c>
+      <c r="D57" s="4">
+        <v>3000052</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="1">
+        <v>4</v>
+      </c>
+      <c r="G57" s="1">
+        <v>7</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:10">
+      <c r="C58" s="1">
+        <v>53</v>
+      </c>
+      <c r="D58" s="4">
+        <v>3000053</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F58" s="1">
+        <v>5</v>
+      </c>
+      <c r="G58" s="1">
+        <v>7</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:10">
+      <c r="C59" s="1">
+        <v>54</v>
+      </c>
+      <c r="D59" s="4">
+        <v>3000054</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F59" s="1">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1">
+        <v>7</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:10">
+      <c r="C60" s="1">
+        <v>55</v>
+      </c>
+      <c r="D60" s="4">
+        <v>3000055</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F60" s="1">
+        <v>7</v>
+      </c>
+      <c r="G60" s="1">
+        <v>7</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:10">
+      <c r="C61" s="1">
+        <v>56</v>
+      </c>
+      <c r="D61" s="4">
+        <v>3000056</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F61" s="1">
+        <v>8</v>
+      </c>
+      <c r="G61" s="1">
+        <v>7</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:10">
+      <c r="C62" s="1">
+        <v>57</v>
+      </c>
+      <c r="D62" s="4">
+        <v>3000057</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" s="1">
+        <v>1</v>
+      </c>
+      <c r="G62" s="1">
+        <v>8</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:10">
+      <c r="C63" s="1">
+        <v>58</v>
+      </c>
+      <c r="D63" s="4">
+        <v>3000058</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F63" s="1">
+        <v>2</v>
+      </c>
+      <c r="G63" s="1">
+        <v>8</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:10">
+      <c r="C64" s="1">
+        <v>59</v>
+      </c>
+      <c r="D64" s="4">
+        <v>3000059</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1">
+        <v>8</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:10">
+      <c r="C65" s="1">
+        <v>60</v>
+      </c>
+      <c r="D65" s="4">
+        <v>3000060</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F65" s="1">
+        <v>4</v>
+      </c>
+      <c r="G65" s="1">
+        <v>8</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:10">
+      <c r="C66" s="1">
+        <v>61</v>
+      </c>
+      <c r="D66" s="4">
+        <v>3000061</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F66" s="1">
+        <v>5</v>
+      </c>
+      <c r="G66" s="1">
+        <v>8</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:10">
+      <c r="C67" s="1">
+        <v>62</v>
+      </c>
+      <c r="D67" s="4">
+        <v>3000062</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67" s="1">
+        <v>6</v>
+      </c>
+      <c r="G67" s="1">
+        <v>8</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:10">
+      <c r="C68" s="1">
+        <v>63</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3000063</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F68" s="1">
+        <v>7</v>
+      </c>
+      <c r="G68" s="1">
+        <v>8</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:10">
+      <c r="C69" s="1">
+        <v>64</v>
+      </c>
+      <c r="D69" s="4">
+        <v>3000064</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8</v>
+      </c>
+      <c r="G69" s="1">
+        <v>8</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:10">
+      <c r="C70" s="1">
+        <v>65</v>
+      </c>
+      <c r="D70" s="4">
+        <v>3000065</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1">
+        <v>9</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:10">
+      <c r="C71" s="1">
+        <v>66</v>
+      </c>
+      <c r="D71" s="4">
+        <v>3000066</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F71" s="1">
+        <v>2</v>
+      </c>
+      <c r="G71" s="1">
+        <v>9</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:10">
+      <c r="C72" s="1">
+        <v>67</v>
+      </c>
+      <c r="D72" s="4">
+        <v>3000067</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F72" s="1">
+        <v>3</v>
+      </c>
+      <c r="G72" s="1">
+        <v>9</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:10">
+      <c r="C73" s="1">
+        <v>68</v>
+      </c>
+      <c r="D73" s="4">
+        <v>3000068</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F73" s="1">
+        <v>4</v>
+      </c>
+      <c r="G73" s="1">
+        <v>9</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:10">
+      <c r="C74" s="1">
+        <v>69</v>
+      </c>
+      <c r="D74" s="4">
+        <v>3000069</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F74" s="1">
+        <v>5</v>
+      </c>
+      <c r="G74" s="1">
+        <v>9</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:10">
+      <c r="C75" s="1">
+        <v>70</v>
+      </c>
+      <c r="D75" s="4">
+        <v>3000070</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F75" s="1">
+        <v>6</v>
+      </c>
+      <c r="G75" s="1">
+        <v>9</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:10">
+      <c r="C76" s="1">
+        <v>71</v>
+      </c>
+      <c r="D76" s="4">
+        <v>3000071</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F76" s="1">
+        <v>7</v>
+      </c>
+      <c r="G76" s="1">
+        <v>9</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:10">
+      <c r="C77" s="1">
+        <v>72</v>
+      </c>
+      <c r="D77" s="4">
+        <v>3000072</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="1">
+        <v>8</v>
+      </c>
+      <c r="G77" s="1">
+        <v>9</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:10">
+      <c r="C78" s="1">
+        <v>73</v>
+      </c>
+      <c r="D78" s="4">
+        <v>3000073</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F78" s="1">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1">
+        <v>10</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:10">
+      <c r="C79" s="1">
+        <v>74</v>
+      </c>
+      <c r="D79" s="4">
+        <v>3000074</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F79" s="1">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1">
+        <v>10</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:10">
+      <c r="C80" s="1">
+        <v>75</v>
+      </c>
+      <c r="D80" s="4">
+        <v>3000075</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F80" s="1">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1">
+        <v>10</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:10">
+      <c r="C81" s="1">
+        <v>76</v>
+      </c>
+      <c r="D81" s="4">
+        <v>3000076</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="1">
+        <v>4</v>
+      </c>
+      <c r="G81" s="1">
+        <v>10</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:10">
+      <c r="C82" s="1">
+        <v>77</v>
+      </c>
+      <c r="D82" s="4">
+        <v>3000077</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F82" s="1">
+        <v>5</v>
+      </c>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:10">
+      <c r="C83" s="1">
+        <v>78</v>
+      </c>
+      <c r="D83" s="4">
+        <v>3000078</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F83" s="1">
+        <v>6</v>
+      </c>
+      <c r="G83" s="1">
+        <v>10</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:10">
+      <c r="C84" s="1">
+        <v>79</v>
+      </c>
+      <c r="D84" s="4">
+        <v>3000079</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F84" s="1">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1">
+        <v>10</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:10">
+      <c r="C85" s="1">
+        <v>80</v>
+      </c>
+      <c r="D85" s="4">
+        <v>3000080</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="1">
+        <v>8</v>
+      </c>
+      <c r="G85" s="1">
+        <v>10</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 H3 I3 J3 D4 E4 F4 G4 H4 I4 J4 D5 E5 F5 G5 H5 I5 J5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="37">
   <si>
     <t>#</t>
   </si>
@@ -56,6 +56,9 @@
     <t>UpAttrValue</t>
   </si>
   <si>
+    <t>ItemId</t>
+  </si>
+  <si>
     <t>Fee</t>
   </si>
   <si>
@@ -74,97 +77,67 @@
     <t>小男战士</t>
   </si>
   <si>
-    <t>2001,2002,2003,2012</t>
-  </si>
-  <si>
-    <t>100,200,300,100</t>
-  </si>
-  <si>
-    <t>10,20,30,10</t>
+    <t>1,2,3,1004</t>
+  </si>
+  <si>
+    <t>10000,50,500,5</t>
   </si>
   <si>
     <t>小女战士</t>
   </si>
   <si>
+    <t>1,2,3,1005</t>
+  </si>
+  <si>
     <t>小男法师</t>
   </si>
   <si>
+    <t>1,2,3,1006</t>
+  </si>
+  <si>
     <t>小女法师</t>
   </si>
   <si>
+    <t>1,2,3,1007</t>
+  </si>
+  <si>
     <t>小男道士</t>
   </si>
   <si>
+    <t>1,2,3,1008</t>
+  </si>
+  <si>
     <t>小女道士</t>
   </si>
   <si>
-    <t>男战士</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,31</t>
-  </si>
-  <si>
-    <t>150,300,450,6</t>
-  </si>
-  <si>
-    <t>女战士</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,32</t>
-  </si>
-  <si>
-    <t>150,300,450,3</t>
-  </si>
-  <si>
-    <t>男法师</t>
-  </si>
-  <si>
-    <t>女法师</t>
-  </si>
-  <si>
-    <t>男道士</t>
-  </si>
-  <si>
-    <t>女道士</t>
-  </si>
-  <si>
-    <t>经验多多</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,50</t>
-  </si>
-  <si>
-    <t>200,400,600,10</t>
-  </si>
-  <si>
-    <t>金币多多</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,51</t>
-  </si>
-  <si>
-    <t>爆率多多</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,52</t>
-  </si>
-  <si>
-    <t>品质高高</t>
-  </si>
-  <si>
-    <t>2001,2002,2003,53</t>
-  </si>
-  <si>
-    <t>TapTap</t>
-  </si>
-  <si>
-    <t>QQ</t>
+    <t>1,2,3,1009</t>
+  </si>
+  <si>
+    <t>Tap玩家</t>
+  </si>
+  <si>
+    <t>1,2,3,1003</t>
+  </si>
+  <si>
+    <t>1000,5,50,1</t>
+  </si>
+  <si>
+    <t>QQ玩家</t>
+  </si>
+  <si>
+    <t>1,2,3,1002</t>
   </si>
   <si>
     <t>老玩家</t>
   </si>
   <si>
+    <t>1,2,3,1001</t>
+  </si>
+  <si>
     <t>大佬再临</t>
+  </si>
+  <si>
+    <t>10000,50,500,10</t>
   </si>
 </sst>
 </file>
@@ -177,7 +150,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +170,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -667,143 +647,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1124,7 +1105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1135,12 +1116,12 @@
     <col min="7" max="7" width="20.0416666666667" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.8083333333333" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="12.8166666666667" style="2" customWidth="1"/>
-    <col min="12" max="16369" width="9" style="2"/>
-    <col min="16370" max="16384" width="9" style="1"/>
+    <col min="10" max="12" width="12.8166666666667" style="2" customWidth="1"/>
+    <col min="13" max="16370" width="9" style="2"/>
+    <col min="16371" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="2"/>
@@ -1150,8 +1131,9 @@
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="2"/>
@@ -1161,8 +1143,9 @@
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1192,12 +1175,15 @@
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1223,68 +1209,77 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:11">
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:11">
+        <v>12</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I6" s="1">
-        <v>2004</v>
+        <v>1004</v>
       </c>
       <c r="J6" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K6" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L6" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1294,630 +1289,447 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="4" t="s">
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I7" s="1">
-        <v>2004</v>
+        <v>1005</v>
       </c>
       <c r="J7" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K7" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L7" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="F8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H8" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I8" s="1">
-        <v>2005</v>
+        <v>1006</v>
       </c>
       <c r="J8" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L8" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="F9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I9" s="1">
-        <v>2005</v>
+        <v>1007</v>
       </c>
       <c r="J9" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L9" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="F10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H10" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I10" s="1">
-        <v>2006</v>
+        <v>1008</v>
       </c>
       <c r="J10" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K10" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L10" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:11">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="F11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="H11" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="I11" s="1">
-        <v>2006</v>
+        <v>1009</v>
       </c>
       <c r="J11" s="1">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="K11" s="1">
+        <v>5003</v>
+      </c>
+      <c r="L11" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="C12" s="1">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="1">
-        <v>31</v>
-      </c>
-      <c r="J12" s="1">
-        <v>20</v>
-      </c>
-      <c r="K12" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="C13" s="1">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="1">
-        <v>32</v>
-      </c>
-      <c r="J13" s="1">
-        <v>10</v>
-      </c>
-      <c r="K13" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="1">
-        <v>31</v>
-      </c>
-      <c r="J14" s="1">
-        <v>20</v>
-      </c>
-      <c r="K14" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="1">
-        <v>32</v>
-      </c>
-      <c r="J15" s="1">
-        <v>10</v>
-      </c>
-      <c r="K15" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="1">
-        <v>31</v>
-      </c>
-      <c r="J16" s="1">
-        <v>20</v>
-      </c>
-      <c r="K16" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:11">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="1">
-        <v>32</v>
-      </c>
-      <c r="J17" s="1">
-        <v>10</v>
-      </c>
-      <c r="K17" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:11">
-      <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="1">
-        <v>50</v>
-      </c>
-      <c r="J18" s="1">
-        <v>10</v>
-      </c>
-      <c r="K18" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:11">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="1">
-        <v>51</v>
-      </c>
-      <c r="J19" s="1">
-        <v>10</v>
-      </c>
-      <c r="K19" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:11">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="1">
-        <v>52</v>
-      </c>
-      <c r="J20" s="1">
-        <v>10</v>
-      </c>
-      <c r="K20" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:11">
-      <c r="C21" s="1">
-        <v>16</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="1">
-        <v>53</v>
-      </c>
-      <c r="J21" s="1">
-        <v>10</v>
-      </c>
-      <c r="K21" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:11">
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:12">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:12">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:12">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" customHeight="1" spans="6:12">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="6:12">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="6:12">
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:11">
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="6:12">
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="6:12">
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="6:12">
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="6:12">
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="6:12">
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="6:12">
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" customHeight="1" spans="6:12">
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:11">
+      <c r="L29" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
       <c r="C37" s="1">
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>17</v>
+      <c r="F37" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="I37" s="1">
-        <v>2004</v>
+        <v>1</v>
       </c>
       <c r="J37" s="1">
-        <v>50</v>
-      </c>
-      <c r="K37" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:11">
+        <v>500</v>
+      </c>
+      <c r="K37" s="4">
+        <v>10001</v>
+      </c>
+      <c r="L37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:12">
       <c r="C38" s="1">
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>17</v>
+      <c r="F38" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="I38" s="1">
-        <v>2004</v>
+        <v>2</v>
       </c>
       <c r="J38" s="1">
-        <v>50</v>
-      </c>
-      <c r="K38" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:11">
+        <v>5</v>
+      </c>
+      <c r="K38" s="4">
+        <v>10002</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
       <c r="C39" s="1">
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>17</v>
+      <c r="F39" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="I39" s="1">
-        <v>2005</v>
+        <v>3</v>
       </c>
       <c r="J39" s="1">
         <v>50</v>
       </c>
-      <c r="K39" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:11">
+      <c r="K39" s="4">
+        <v>10003</v>
+      </c>
+      <c r="L39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1">
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>17</v>
+      <c r="F40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="I40" s="1">
-        <v>2005</v>
+        <v>1003</v>
       </c>
       <c r="J40" s="1">
-        <v>50</v>
-      </c>
-      <c r="K40" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:11">
+      <c r="K40" s="4">
+        <v>10004</v>
+      </c>
+      <c r="L40" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:11">
+      <c r="K41" s="4"/>
+      <c r="L41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 C5:D5 E5 F5:H5 J5:K5 C3:D4 F3:K4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3 K4 C5:H5 J5 K5 L5 L3:L4 C3:J4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -77,7 +77,10 @@
     <t>小男战士</t>
   </si>
   <si>
-    <t>1,2,3,1004</t>
+    <t>1,2,3,92</t>
+  </si>
+  <si>
+    <t>10000,50,500,1</t>
   </si>
   <si>
     <t>10000,50,500,5</t>
@@ -86,52 +89,28 @@
     <t>小女战士</t>
   </si>
   <si>
-    <t>1,2,3,1005</t>
-  </si>
-  <si>
     <t>小男法师</t>
   </si>
   <si>
-    <t>1,2,3,1006</t>
-  </si>
-  <si>
     <t>小女法师</t>
   </si>
   <si>
-    <t>1,2,3,1007</t>
-  </si>
-  <si>
     <t>小男道士</t>
   </si>
   <si>
-    <t>1,2,3,1008</t>
-  </si>
-  <si>
     <t>小女道士</t>
   </si>
   <si>
-    <t>1,2,3,1009</t>
-  </si>
-  <si>
     <t>Tap玩家</t>
   </si>
   <si>
-    <t>1,2,3,1003</t>
-  </si>
-  <si>
     <t>1000,5,50,1</t>
   </si>
   <si>
     <t>QQ玩家</t>
   </si>
   <si>
-    <t>1,2,3,1002</t>
-  </si>
-  <si>
     <t>老玩家</t>
-  </si>
-  <si>
-    <t>1,2,3,1001</t>
   </si>
   <si>
     <t>大佬再临</t>
@@ -1264,7 +1243,7 @@
         <v>17</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="1">
         <v>1004</v>
@@ -1284,19 +1263,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="1">
         <v>1005</v>
@@ -1322,13 +1301,13 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1">
         <v>1006</v>
@@ -1348,19 +1327,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" s="1">
         <v>1007</v>
@@ -1380,19 +1359,19 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1">
         <v>1008</v>
@@ -1412,19 +1391,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1">
         <v>1009</v>
@@ -1588,19 +1567,19 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
@@ -1620,19 +1599,19 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I38" s="1">
         <v>2</v>
@@ -1652,19 +1631,19 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I39" s="1">
         <v>3</v>
@@ -1684,19 +1663,19 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="I40" s="1">
         <v>1003</v>
@@ -1729,7 +1708,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3 K4 C5:H5 J5 K5 L5 L3:L4 C3:J4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C5:H5 J5:L5 C3:L4" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -80,10 +80,7 @@
     <t>1,2,3,92</t>
   </si>
   <si>
-    <t>10000,50,500,1</t>
-  </si>
-  <si>
-    <t>10000,50,500,5</t>
+    <t>25000,250,250,2</t>
   </si>
   <si>
     <t>小女战士</t>
@@ -104,7 +101,7 @@
     <t>Tap玩家</t>
   </si>
   <si>
-    <t>1000,5,50,1</t>
+    <t>5000,100,100,1</t>
   </si>
   <si>
     <t>QQ玩家</t>
@@ -116,7 +113,7 @@
     <t>大佬再临</t>
   </si>
   <si>
-    <t>10000,50,500,10</t>
+    <t>50000,500,500,5</t>
   </si>
 </sst>
 </file>
@@ -1243,7 +1240,7 @@
         <v>17</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1">
         <v>1004</v>
@@ -1263,7 +1260,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1275,7 +1272,7 @@
         <v>17</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1">
         <v>1005</v>
@@ -1295,7 +1292,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1307,7 +1304,7 @@
         <v>17</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1">
         <v>1006</v>
@@ -1327,7 +1324,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1339,7 +1336,7 @@
         <v>17</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1">
         <v>1007</v>
@@ -1359,7 +1356,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1371,7 +1368,7 @@
         <v>17</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1">
         <v>1008</v>
@@ -1391,7 +1388,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1403,7 +1400,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1">
         <v>1009</v>
@@ -1567,7 +1564,7 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
@@ -1576,16 +1573,16 @@
         <v>16</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I37" s="1">
         <v>1</v>
       </c>
       <c r="J37" s="1">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="K37" s="4">
         <v>10001</v>
@@ -1599,7 +1596,7 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -1608,16 +1605,16 @@
         <v>16</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I38" s="1">
         <v>2</v>
       </c>
       <c r="J38" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K38" s="4">
         <v>10002</v>
@@ -1631,7 +1628,7 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -1640,16 +1637,16 @@
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I39" s="1">
         <v>3</v>
       </c>
       <c r="J39" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K39" s="4">
         <v>10003</v>
@@ -1663,7 +1660,7 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -1672,10 +1669,10 @@
         <v>16</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I40" s="1">
         <v>1003</v>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -80,7 +80,7 @@
     <t>1,2,3,92</t>
   </si>
   <si>
-    <t>25000,250,250,2</t>
+    <t>50000,500,500,2</t>
   </si>
   <si>
     <t>小女战士</t>
@@ -92,6 +92,9 @@
     <t>小女法师</t>
   </si>
   <si>
+    <t>75000,1000,1000,3</t>
+  </si>
+  <si>
     <t>小男道士</t>
   </si>
   <si>
@@ -101,7 +104,7 @@
     <t>Tap玩家</t>
   </si>
   <si>
-    <t>5000,100,100,1</t>
+    <t>10000,200,200,1</t>
   </si>
   <si>
     <t>QQ玩家</t>
@@ -113,7 +116,7 @@
     <t>大佬再临</t>
   </si>
   <si>
-    <t>50000,500,500,5</t>
+    <t>100000,2000,2000,5</t>
   </si>
 </sst>
 </file>
@@ -1333,10 +1336,10 @@
         <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I9" s="1">
         <v>1007</v>
@@ -1348,7 +1351,7 @@
         <v>5003</v>
       </c>
       <c r="L9" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -1356,7 +1359,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -1365,10 +1368,10 @@
         <v>16</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1">
         <v>1008</v>
@@ -1380,7 +1383,7 @@
         <v>5003</v>
       </c>
       <c r="L10" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -1388,7 +1391,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1397,10 +1400,10 @@
         <v>16</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1">
         <v>1009</v>
@@ -1412,7 +1415,7 @@
         <v>5003</v>
       </c>
       <c r="L11" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:12">
@@ -1564,7 +1567,7 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
@@ -1573,16 +1576,16 @@
         <v>16</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="J37" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K37" s="4">
         <v>10001</v>
@@ -1596,7 +1599,7 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -1605,16 +1608,16 @@
         <v>16</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I38" s="1">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K38" s="4">
         <v>10002</v>
@@ -1628,7 +1631,7 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -1637,16 +1640,16 @@
         <v>16</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I39" s="1">
-        <v>3</v>
+        <v>1003</v>
       </c>
       <c r="J39" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K39" s="4">
         <v>10003</v>
@@ -1660,7 +1663,7 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -1669,13 +1672,13 @@
         <v>16</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I40" s="1">
-        <v>1003</v>
+        <v>2003</v>
       </c>
       <c r="J40" s="1">
         <v>10</v>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -77,25 +77,28 @@
     <t>小男战士</t>
   </si>
   <si>
+    <t>1001,1002,1003,92</t>
+  </si>
+  <si>
+    <t>20,10,10,2</t>
+  </si>
+  <si>
+    <t>小女战士</t>
+  </si>
+  <si>
+    <t>小男法师</t>
+  </si>
+  <si>
+    <t>小女法师</t>
+  </si>
+  <si>
+    <t>小男道士</t>
+  </si>
+  <si>
     <t>1,2,3,92</t>
   </si>
   <si>
-    <t>50000,500,500,2</t>
-  </si>
-  <si>
-    <t>小女战士</t>
-  </si>
-  <si>
-    <t>小男法师</t>
-  </si>
-  <si>
-    <t>小女法师</t>
-  </si>
-  <si>
     <t>75000,1000,1000,3</t>
-  </si>
-  <si>
-    <t>小男道士</t>
   </si>
   <si>
     <t>小女道士</t>
@@ -1246,10 +1249,10 @@
         <v>17</v>
       </c>
       <c r="I6" s="1">
-        <v>1004</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6" s="1">
         <v>5003</v>
@@ -1278,10 +1281,10 @@
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>1005</v>
+        <v>11</v>
       </c>
       <c r="J7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K7" s="1">
         <v>5003</v>
@@ -1310,10 +1313,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="1">
-        <v>1006</v>
+        <v>13</v>
       </c>
       <c r="J8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
         <v>5003</v>
@@ -1336,16 +1339,16 @@
         <v>16</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1">
-        <v>1007</v>
+        <v>14</v>
       </c>
       <c r="J9" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K9" s="1">
         <v>5003</v>
@@ -1355,23 +1358,29 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I10" s="1">
         <v>1008</v>
@@ -1387,23 +1396,29 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I11" s="1">
         <v>1009</v>
@@ -1567,19 +1582,19 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I37" s="1">
         <v>1001</v>
@@ -1599,19 +1614,19 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I38" s="1">
         <v>1002</v>
@@ -1631,19 +1646,19 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I39" s="1">
         <v>1003</v>
@@ -1663,19 +1678,19 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1">
         <v>2003</v>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1709,6 +1709,7 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="4"/>
       <c r="L41" s="1"/>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
   <si>
     <t>#</t>
   </si>
@@ -83,15 +83,27 @@
     <t>20,10,10,2</t>
   </si>
   <si>
+    <t>物攻</t>
+  </si>
+  <si>
     <t>小女战士</t>
   </si>
   <si>
+    <t>魔法</t>
+  </si>
+  <si>
     <t>小男法师</t>
   </si>
   <si>
+    <t>道术</t>
+  </si>
+  <si>
     <t>小女法师</t>
   </si>
   <si>
+    <t>生命</t>
+  </si>
+  <si>
     <t>小男道士</t>
   </si>
   <si>
@@ -99,6 +111,9 @@
   </si>
   <si>
     <t>75000,1000,1000,3</t>
+  </si>
+  <si>
+    <t>防御</t>
   </si>
   <si>
     <t>小女道士</t>
@@ -1087,7 +1102,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1103,7 +1118,7 @@
     <col min="16371" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="2"/>
@@ -1114,8 +1129,11 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="2"/>
@@ -1126,8 +1144,11 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1161,7 +1182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
@@ -1195,7 +1216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
@@ -1229,7 +1250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1249,10 +1270,10 @@
         <v>17</v>
       </c>
       <c r="I6" s="1">
-        <v>10</v>
+        <v>1007</v>
       </c>
       <c r="J6" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K6" s="1">
         <v>5003</v>
@@ -1260,13 +1281,16 @@
       <c r="L6" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1281,10 +1305,10 @@
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>11</v>
+        <v>1008</v>
       </c>
       <c r="J7" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K7" s="1">
         <v>5003</v>
@@ -1292,13 +1316,16 @@
       <c r="L7" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1313,10 +1340,10 @@
         <v>17</v>
       </c>
       <c r="I8" s="1">
-        <v>13</v>
+        <v>1009</v>
       </c>
       <c r="J8" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K8" s="1">
         <v>5003</v>
@@ -1324,13 +1351,16 @@
       <c r="L8" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M8" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -1345,19 +1375,22 @@
         <v>17</v>
       </c>
       <c r="I9" s="1">
-        <v>14</v>
+        <v>1001</v>
       </c>
       <c r="J9" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1">
         <v>5003</v>
       </c>
       <c r="L9" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>10</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,22 +1401,22 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="J10" s="1">
         <v>5</v>
@@ -1392,10 +1425,13 @@
         <v>5003</v>
       </c>
       <c r="L10" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,22 +1442,22 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="J11" s="1">
         <v>5</v>
@@ -1433,7 +1469,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:12">
+    <row r="12" customHeight="1" spans="1:13">
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1441,7 +1477,7 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" customHeight="1" spans="1:12">
+    <row r="13" customHeight="1" spans="1:13">
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1449,7 +1485,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" customHeight="1" spans="1:12">
+    <row r="14" customHeight="1" spans="1:13">
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1457,7 +1493,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" customHeight="1" spans="1:12">
+    <row r="15" customHeight="1" spans="1:13">
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1465,7 +1501,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" customHeight="1" spans="1:12">
+    <row r="16" customHeight="1" spans="1:13">
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1582,19 +1618,19 @@
         <v>101</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I37" s="1">
         <v>1001</v>
@@ -1614,19 +1650,19 @@
         <v>102</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I38" s="1">
         <v>1002</v>
@@ -1646,19 +1682,19 @@
         <v>103</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I39" s="1">
         <v>1003</v>
@@ -1678,19 +1714,19 @@
         <v>104</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I40" s="1">
         <v>2003</v>
@@ -1709,7 +1745,6 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="4"/>
       <c r="L41" s="1"/>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -128,10 +128,10 @@
     <t>QQ玩家</t>
   </si>
   <si>
-    <t>老玩家</t>
-  </si>
-  <si>
-    <t>大佬再临</t>
+    <t>无尽玩家</t>
+  </si>
+  <si>
+    <t>天下无敌</t>
   </si>
   <si>
     <t>100000,2000,2000,5</t>

--- a/Excel/FashionConfig.xlsx
+++ b/Excel/FashionConfig.xlsx
@@ -1270,10 +1270,10 @@
         <v>17</v>
       </c>
       <c r="I6" s="1">
-        <v>1007</v>
+        <v>27</v>
       </c>
       <c r="J6" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1">
         <v>5003</v>
@@ -1305,7 +1305,7 @@
         <v>17</v>
       </c>
       <c r="I7" s="1">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="J7" s="1">
         <v>20</v>
@@ -1340,7 +1340,7 @@
         <v>17</v>
       </c>
       <c r="I8" s="1">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="J8" s="1">
         <v>20</v>
@@ -1375,10 +1375,10 @@
         <v>17</v>
       </c>
       <c r="I9" s="1">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="J9" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1">
         <v>5003</v>
